--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125920695</v>
+        <v>125923757</v>
       </c>
       <c r="B2" t="n">
-        <v>98328</v>
+        <v>98331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -703,20 +703,28 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>795427</v>
+        <v>795428</v>
       </c>
       <c r="R2" t="n">
-        <v>7292083</v>
+        <v>7292065</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,25 +762,26 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125920335</v>
+        <v>125923704</v>
       </c>
       <c r="B3" t="n">
         <v>78999</v>
@@ -801,19 +810,22 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>795428</v>
+        <v>795285</v>
       </c>
       <c r="R3" t="n">
-        <v>7292266</v>
+        <v>7291972</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,75 +863,70 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125919207</v>
+        <v>125923592</v>
       </c>
       <c r="B4" t="n">
-        <v>98328</v>
+        <v>78999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>795334</v>
+        <v>795338</v>
       </c>
       <c r="R4" t="n">
-        <v>7291988</v>
+        <v>7292144</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,74 +964,67 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125923757</v>
+        <v>125920247</v>
       </c>
       <c r="B5" t="n">
-        <v>98328</v>
+        <v>78999</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>795428</v>
+        <v>795441</v>
       </c>
       <c r="R5" t="n">
-        <v>7292065</v>
+        <v>7292235</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1062,29 +1062,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125923704</v>
+        <v>125920370</v>
       </c>
       <c r="B6" t="n">
-        <v>78999</v>
+        <v>78967</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,40 +1091,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>795285</v>
+        <v>795431</v>
       </c>
       <c r="R6" t="n">
-        <v>7291972</v>
+        <v>7292149</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1163,56 +1159,60 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125923592</v>
+        <v>125923656</v>
       </c>
       <c r="B7" t="n">
-        <v>78999</v>
+        <v>98331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>795338</v>
+        <v>795314</v>
       </c>
       <c r="R7" t="n">
-        <v>7292144</v>
+        <v>7292056</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1283,48 +1283,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125920370</v>
+        <v>125923682</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>795431</v>
+        <v>795317</v>
       </c>
       <c r="R8" t="n">
-        <v>7292149</v>
+        <v>7292007</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1362,63 +1370,73 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125920247</v>
+        <v>125919680</v>
       </c>
       <c r="B9" t="n">
-        <v>78999</v>
+        <v>98331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>795441</v>
+        <v>795340</v>
       </c>
       <c r="R9" t="n">
-        <v>7292235</v>
+        <v>7292160</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1477,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125923656</v>
+        <v>125923769</v>
       </c>
       <c r="B10" t="n">
-        <v>98328</v>
+        <v>98331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,7 +1525,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -1516,14 +1534,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Skog , Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>795314</v>
+        <v>795443</v>
       </c>
       <c r="R10" t="n">
-        <v>7292056</v>
+        <v>7292063</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1583,56 +1601,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125923682</v>
+        <v>125920922</v>
       </c>
       <c r="B11" t="n">
-        <v>98328</v>
+        <v>78999</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>795317</v>
+        <v>795257</v>
       </c>
       <c r="R11" t="n">
-        <v>7292007</v>
+        <v>7292021</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1670,76 +1680,74 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125919680</v>
+        <v>125923482</v>
       </c>
       <c r="B12" t="n">
-        <v>98328</v>
+        <v>98352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>795340</v>
+        <v>795454</v>
       </c>
       <c r="R12" t="n">
-        <v>7292160</v>
+        <v>7292235</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1777,28 +1785,29 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125920922</v>
+        <v>125923834</v>
       </c>
       <c r="B13" t="n">
-        <v>78999</v>
+        <v>91227</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1806,37 +1815,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>795257</v>
+        <v>795428</v>
       </c>
       <c r="R13" t="n">
-        <v>7292021</v>
+        <v>7292065</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1874,28 +1886,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125923769</v>
+        <v>125923726</v>
       </c>
       <c r="B14" t="n">
-        <v>98328</v>
+        <v>98331</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1922,7 +1935,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -1931,14 +1944,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skog , Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>795443</v>
+        <v>795291</v>
       </c>
       <c r="R14" t="n">
-        <v>7292063</v>
+        <v>7291954</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1998,56 +2011,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125923726</v>
+        <v>125920880</v>
       </c>
       <c r="B15" t="n">
-        <v>98328</v>
+        <v>78999</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>795291</v>
+        <v>795280</v>
       </c>
       <c r="R15" t="n">
-        <v>7291954</v>
+        <v>7292044</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2085,61 +2090,55 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125923482</v>
+        <v>125923669</v>
       </c>
       <c r="B16" t="n">
-        <v>98349</v>
+        <v>78999</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2147,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>795454</v>
+        <v>795323</v>
       </c>
       <c r="R16" t="n">
-        <v>7292235</v>
+        <v>7292029</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2210,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125923834</v>
+        <v>125923612</v>
       </c>
       <c r="B17" t="n">
-        <v>91224</v>
+        <v>78999</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2221,21 +2220,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2248,13 +2247,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>795428</v>
+        <v>795337</v>
       </c>
       <c r="R17" t="n">
-        <v>7292065</v>
+        <v>7292137</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2311,48 +2310,56 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125920880</v>
+        <v>125923558</v>
       </c>
       <c r="B18" t="n">
-        <v>78999</v>
+        <v>98331</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>795280</v>
+        <v>795338</v>
       </c>
       <c r="R18" t="n">
-        <v>7292044</v>
+        <v>7292138</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2390,28 +2397,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125919136</v>
+        <v>125923742</v>
       </c>
       <c r="B19" t="n">
-        <v>98328</v>
+        <v>98331</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2438,27 +2446,26 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>795292</v>
+        <v>795310</v>
       </c>
       <c r="R19" t="n">
-        <v>7291953</v>
+        <v>7291958</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2496,55 +2503,61 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125923612</v>
+        <v>125923795</v>
       </c>
       <c r="B20" t="n">
-        <v>78999</v>
+        <v>98331</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2552,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>795337</v>
+        <v>795418</v>
       </c>
       <c r="R20" t="n">
-        <v>7292137</v>
+        <v>7292007</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2615,42 +2628,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125923558</v>
+        <v>125923694</v>
       </c>
       <c r="B21" t="n">
-        <v>98328</v>
+        <v>78999</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2658,10 +2666,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>795338</v>
+        <v>795304</v>
       </c>
       <c r="R21" t="n">
-        <v>7292138</v>
+        <v>7291985</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2721,51 +2729,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125923669</v>
+        <v>125920167</v>
       </c>
       <c r="B22" t="n">
-        <v>78999</v>
+        <v>79974</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>795323</v>
+        <v>795457</v>
       </c>
       <c r="R22" t="n">
-        <v>7292029</v>
+        <v>7292262</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2803,61 +2808,55 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125923742</v>
+        <v>125923644</v>
       </c>
       <c r="B23" t="n">
-        <v>98328</v>
+        <v>78999</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2865,10 +2864,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>795310</v>
+        <v>795314</v>
       </c>
       <c r="R23" t="n">
-        <v>7291958</v>
+        <v>7292076</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2928,10 +2927,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125923795</v>
+        <v>125923784</v>
       </c>
       <c r="B24" t="n">
-        <v>98328</v>
+        <v>98331</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2958,7 +2957,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -2971,10 +2970,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>795418</v>
+        <v>795425</v>
       </c>
       <c r="R24" t="n">
-        <v>7292007</v>
+        <v>7292015</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3034,7 +3033,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125923694</v>
+        <v>125920335</v>
       </c>
       <c r="B25" t="n">
         <v>78999</v>
@@ -3063,22 +3062,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>795304</v>
+        <v>795428</v>
       </c>
       <c r="R25" t="n">
-        <v>7291985</v>
+        <v>7292266</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3116,70 +3112,66 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Erik Christiansson, Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125923644</v>
+        <v>125920695</v>
       </c>
       <c r="B26" t="n">
-        <v>78999</v>
+        <v>98331</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>795314</v>
+        <v>795427</v>
       </c>
       <c r="R26" t="n">
-        <v>7292076</v>
+        <v>7292083</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3217,64 +3209,72 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Erik Christiansson, Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125920167</v>
+        <v>125919207</v>
       </c>
       <c r="B27" t="n">
-        <v>79974</v>
+        <v>98331</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>795457</v>
+        <v>795334</v>
       </c>
       <c r="R27" t="n">
-        <v>7292262</v>
+        <v>7291988</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3321,22 +3321,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Erik Christiansson, Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125920110</v>
+        <v>125919136</v>
       </c>
       <c r="B28" t="n">
-        <v>98328</v>
+        <v>98331</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3363,19 +3363,24 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>795428</v>
+        <v>795292</v>
       </c>
       <c r="R28" t="n">
-        <v>7292266</v>
+        <v>7291953</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3427,17 +3432,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erik Christiansson</t>
+          <t>Erik Christiansson, Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125923784</v>
+        <v>125920110</v>
       </c>
       <c r="B29" t="n">
-        <v>98328</v>
+        <v>98331</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3464,26 +3469,22 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>795425</v>
+        <v>795428</v>
       </c>
       <c r="R29" t="n">
-        <v>7292015</v>
+        <v>7292266</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3521,19 +3522,18 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Erik Christiansson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Erik Christiansson, Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -1495,56 +1495,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125923769</v>
+        <v>125920922</v>
       </c>
       <c r="B10" t="n">
-        <v>98331</v>
+        <v>78999</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skog , Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>795443</v>
+        <v>795257</v>
       </c>
       <c r="R10" t="n">
-        <v>7292063</v>
+        <v>7292021</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1582,67 +1574,74 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125920922</v>
+        <v>125923769</v>
       </c>
       <c r="B11" t="n">
-        <v>78999</v>
+        <v>98331</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Skog , Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>795257</v>
+        <v>795443</v>
       </c>
       <c r="R11" t="n">
-        <v>7292021</v>
+        <v>7292063</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1680,18 +1679,19 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2108,37 +2108,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125923669</v>
+        <v>125923558</v>
       </c>
       <c r="B16" t="n">
-        <v>78999</v>
+        <v>98331</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2146,10 +2151,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>795323</v>
+        <v>795338</v>
       </c>
       <c r="R16" t="n">
-        <v>7292029</v>
+        <v>7292138</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2209,7 +2214,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125923612</v>
+        <v>125923669</v>
       </c>
       <c r="B17" t="n">
         <v>78999</v>
@@ -2247,10 +2252,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>795337</v>
+        <v>795323</v>
       </c>
       <c r="R17" t="n">
-        <v>7292137</v>
+        <v>7292029</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2310,42 +2315,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125923558</v>
+        <v>125923612</v>
       </c>
       <c r="B18" t="n">
-        <v>98331</v>
+        <v>78999</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>795338</v>
+        <v>795337</v>
       </c>
       <c r="R18" t="n">
-        <v>7292138</v>
+        <v>7292137</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125923757</v>
       </c>
       <c r="B2" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>125923704</v>
       </c>
       <c r="B3" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>125923592</v>
       </c>
       <c r="B4" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>125920247</v>
       </c>
       <c r="B5" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>125920370</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>125923656</v>
       </c>
       <c r="B7" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>125923682</v>
       </c>
       <c r="B8" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>125919680</v>
       </c>
       <c r="B9" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>125920922</v>
       </c>
       <c r="B10" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>125923769</v>
       </c>
       <c r="B11" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,42 +1698,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125923482</v>
+        <v>125923834</v>
       </c>
       <c r="B12" t="n">
-        <v>98352</v>
+        <v>91228</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1741,13 +1736,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>795454</v>
+        <v>795428</v>
       </c>
       <c r="R12" t="n">
-        <v>7292235</v>
+        <v>7292065</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1804,37 +1799,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125923834</v>
+        <v>125923726</v>
       </c>
       <c r="B13" t="n">
-        <v>91227</v>
+        <v>98332</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>795428</v>
+        <v>795291</v>
       </c>
       <c r="R13" t="n">
-        <v>7292065</v>
+        <v>7291954</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1905,37 +1905,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125923726</v>
+        <v>125923482</v>
       </c>
       <c r="B14" t="n">
-        <v>98331</v>
+        <v>98353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>795291</v>
+        <v>795454</v>
       </c>
       <c r="R14" t="n">
-        <v>7291954</v>
+        <v>7292235</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2014,7 +2014,7 @@
         <v>125920880</v>
       </c>
       <c r="B15" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2108,42 +2108,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125923558</v>
+        <v>125923669</v>
       </c>
       <c r="B16" t="n">
-        <v>98331</v>
+        <v>79000</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2151,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>795338</v>
+        <v>795323</v>
       </c>
       <c r="R16" t="n">
-        <v>7292138</v>
+        <v>7292029</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2214,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125923669</v>
+        <v>125923612</v>
       </c>
       <c r="B17" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,10 +2247,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>795323</v>
+        <v>795337</v>
       </c>
       <c r="R17" t="n">
-        <v>7292029</v>
+        <v>7292137</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2315,37 +2310,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125923612</v>
+        <v>125923558</v>
       </c>
       <c r="B18" t="n">
-        <v>78999</v>
+        <v>98332</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>795337</v>
+        <v>795338</v>
       </c>
       <c r="R18" t="n">
-        <v>7292137</v>
+        <v>7292138</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2419,7 +2419,7 @@
         <v>125923742</v>
       </c>
       <c r="B19" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2522,42 +2522,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125923795</v>
+        <v>125923694</v>
       </c>
       <c r="B20" t="n">
-        <v>98331</v>
+        <v>79000</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2565,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>795418</v>
+        <v>795304</v>
       </c>
       <c r="R20" t="n">
-        <v>7292007</v>
+        <v>7291985</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2628,37 +2623,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125923694</v>
+        <v>125923795</v>
       </c>
       <c r="B21" t="n">
-        <v>78999</v>
+        <v>98332</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>795304</v>
+        <v>795418</v>
       </c>
       <c r="R21" t="n">
-        <v>7291985</v>
+        <v>7292007</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2729,48 +2729,51 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125920167</v>
+        <v>125923644</v>
       </c>
       <c r="B22" t="n">
-        <v>79974</v>
+        <v>79000</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>795457</v>
+        <v>795314</v>
       </c>
       <c r="R22" t="n">
-        <v>7292262</v>
+        <v>7292076</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2808,69 +2811,67 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125923644</v>
+        <v>125920167</v>
       </c>
       <c r="B23" t="n">
-        <v>78999</v>
+        <v>79975</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>795314</v>
+        <v>795457</v>
       </c>
       <c r="R23" t="n">
-        <v>7292076</v>
+        <v>7292262</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2908,19 +2909,18 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2930,7 +2930,7 @@
         <v>125923784</v>
       </c>
       <c r="B24" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>125920335</v>
       </c>
       <c r="B25" t="n">
-        <v>78999</v>
+        <v>79000</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>125920695</v>
       </c>
       <c r="B26" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>125919207</v>
       </c>
       <c r="B27" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>125919136</v>
       </c>
       <c r="B28" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>125920110</v>
       </c>
       <c r="B29" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125923757</v>
       </c>
       <c r="B2" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125923704</v>
+        <v>125920370</v>
       </c>
       <c r="B3" t="n">
-        <v>79000</v>
+        <v>78968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,40 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>795285</v>
+        <v>795431</v>
       </c>
       <c r="R3" t="n">
-        <v>7291972</v>
+        <v>7292149</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,26 +860,25 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125923592</v>
+        <v>125923704</v>
       </c>
       <c r="B4" t="n">
         <v>79000</v>
@@ -920,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>795338</v>
+        <v>795285</v>
       </c>
       <c r="R4" t="n">
-        <v>7292144</v>
+        <v>7291972</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -983,7 +979,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125920247</v>
+        <v>125923592</v>
       </c>
       <c r="B5" t="n">
         <v>79000</v>
@@ -1012,19 +1008,22 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>795441</v>
+        <v>795338</v>
       </c>
       <c r="R5" t="n">
-        <v>7292235</v>
+        <v>7292144</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1062,28 +1061,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125920370</v>
+        <v>125920247</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>79000</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,34 +1091,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>795431</v>
+        <v>795441</v>
       </c>
       <c r="R6" t="n">
-        <v>7292149</v>
+        <v>7292235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,7 +1180,7 @@
         <v>125923656</v>
       </c>
       <c r="B7" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>125923682</v>
       </c>
       <c r="B8" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>125919680</v>
       </c>
       <c r="B9" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>125923769</v>
       </c>
       <c r="B11" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,37 +1698,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125923834</v>
+        <v>125923726</v>
       </c>
       <c r="B12" t="n">
-        <v>91228</v>
+        <v>98334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1736,13 +1741,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>795428</v>
+        <v>795291</v>
       </c>
       <c r="R12" t="n">
-        <v>7292065</v>
+        <v>7291954</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1799,37 +1804,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125923726</v>
+        <v>125923482</v>
       </c>
       <c r="B13" t="n">
-        <v>98332</v>
+        <v>98355</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1842,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>795291</v>
+        <v>795454</v>
       </c>
       <c r="R13" t="n">
-        <v>7291954</v>
+        <v>7292235</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1905,42 +1910,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125923482</v>
+        <v>125923834</v>
       </c>
       <c r="B14" t="n">
-        <v>98353</v>
+        <v>91228</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>795454</v>
+        <v>795428</v>
       </c>
       <c r="R14" t="n">
-        <v>7292235</v>
+        <v>7292065</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>125923558</v>
       </c>
       <c r="B18" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>125923742</v>
       </c>
       <c r="B19" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>125923795</v>
       </c>
       <c r="B21" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2729,51 +2729,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125923644</v>
+        <v>125920167</v>
       </c>
       <c r="B22" t="n">
-        <v>79000</v>
+        <v>79975</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>795314</v>
+        <v>795457</v>
       </c>
       <c r="R22" t="n">
-        <v>7292076</v>
+        <v>7292262</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2811,67 +2808,69 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125920167</v>
+        <v>125923644</v>
       </c>
       <c r="B23" t="n">
-        <v>79975</v>
+        <v>79000</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>795457</v>
+        <v>795314</v>
       </c>
       <c r="R23" t="n">
-        <v>7292262</v>
+        <v>7292076</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2909,18 +2908,19 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2930,7 +2930,7 @@
         <v>125923784</v>
       </c>
       <c r="B24" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>125920695</v>
       </c>
       <c r="B26" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>125919207</v>
       </c>
       <c r="B27" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>125919136</v>
       </c>
       <c r="B28" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>125920110</v>
       </c>
       <c r="B29" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -1495,48 +1495,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125920922</v>
+        <v>125923769</v>
       </c>
       <c r="B10" t="n">
-        <v>79000</v>
+        <v>98334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Skog , Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>795257</v>
+        <v>795443</v>
       </c>
       <c r="R10" t="n">
-        <v>7292021</v>
+        <v>7292063</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1574,74 +1582,67 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125923769</v>
+        <v>125920922</v>
       </c>
       <c r="B11" t="n">
-        <v>98334</v>
+        <v>79000</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skog , Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>795443</v>
+        <v>795257</v>
       </c>
       <c r="R11" t="n">
-        <v>7292063</v>
+        <v>7292021</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1679,19 +1680,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2522,37 +2522,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125923694</v>
+        <v>125923795</v>
       </c>
       <c r="B20" t="n">
-        <v>79000</v>
+        <v>98334</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2560,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>795304</v>
+        <v>795418</v>
       </c>
       <c r="R20" t="n">
-        <v>7291985</v>
+        <v>7292007</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2623,42 +2628,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125923795</v>
+        <v>125923694</v>
       </c>
       <c r="B21" t="n">
-        <v>98334</v>
+        <v>79000</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>795418</v>
+        <v>795304</v>
       </c>
       <c r="R21" t="n">
-        <v>7292007</v>
+        <v>7291985</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125923757</v>
       </c>
       <c r="B2" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>125920370</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>125923704</v>
       </c>
       <c r="B4" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>125923592</v>
       </c>
       <c r="B5" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>125920247</v>
       </c>
       <c r="B6" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>125923656</v>
       </c>
       <c r="B7" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>125923682</v>
       </c>
       <c r="B8" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>125919680</v>
       </c>
       <c r="B9" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,56 +1495,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125923769</v>
+        <v>125920922</v>
       </c>
       <c r="B10" t="n">
-        <v>98334</v>
+        <v>79004</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skog , Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>795443</v>
+        <v>795257</v>
       </c>
       <c r="R10" t="n">
-        <v>7292063</v>
+        <v>7292021</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1582,67 +1574,74 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125920922</v>
+        <v>125923769</v>
       </c>
       <c r="B11" t="n">
-        <v>79000</v>
+        <v>98338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Skog , Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>795257</v>
+        <v>795443</v>
       </c>
       <c r="R11" t="n">
-        <v>7292021</v>
+        <v>7292063</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1680,60 +1679,56 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125923726</v>
+        <v>125923834</v>
       </c>
       <c r="B12" t="n">
-        <v>98334</v>
+        <v>91232</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1741,13 +1736,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>795291</v>
+        <v>795428</v>
       </c>
       <c r="R12" t="n">
-        <v>7291954</v>
+        <v>7292065</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1804,37 +1799,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125923482</v>
+        <v>125923726</v>
       </c>
       <c r="B13" t="n">
-        <v>98355</v>
+        <v>98338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1847,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>795454</v>
+        <v>795291</v>
       </c>
       <c r="R13" t="n">
-        <v>7292235</v>
+        <v>7291954</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1910,37 +1905,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125923834</v>
+        <v>125923482</v>
       </c>
       <c r="B14" t="n">
-        <v>91228</v>
+        <v>98359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>795428</v>
+        <v>795454</v>
       </c>
       <c r="R14" t="n">
-        <v>7292065</v>
+        <v>7292235</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>125920880</v>
       </c>
       <c r="B15" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>125923669</v>
       </c>
       <c r="B16" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>125923612</v>
       </c>
       <c r="B17" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>125923558</v>
       </c>
       <c r="B18" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>125923742</v>
       </c>
       <c r="B19" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2522,42 +2522,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125923795</v>
+        <v>125923694</v>
       </c>
       <c r="B20" t="n">
-        <v>98334</v>
+        <v>79004</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2565,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>795418</v>
+        <v>795304</v>
       </c>
       <c r="R20" t="n">
-        <v>7292007</v>
+        <v>7291985</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2628,37 +2623,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125923694</v>
+        <v>125923795</v>
       </c>
       <c r="B21" t="n">
-        <v>79000</v>
+        <v>98338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>795304</v>
+        <v>795418</v>
       </c>
       <c r="R21" t="n">
-        <v>7291985</v>
+        <v>7292007</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2732,7 +2732,7 @@
         <v>125920167</v>
       </c>
       <c r="B22" t="n">
-        <v>79975</v>
+        <v>79979</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>125923644</v>
       </c>
       <c r="B23" t="n">
-        <v>79000</v>
+        <v>79004</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>125923784</v>
       </c>
       <c r="B24" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,45 +3033,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125920335</v>
+        <v>125920695</v>
       </c>
       <c r="B25" t="n">
-        <v>79000</v>
+        <v>98338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>795428</v>
+        <v>795427</v>
       </c>
       <c r="R25" t="n">
-        <v>7292266</v>
+        <v>7292083</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3130,45 +3130,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125920695</v>
+        <v>125920335</v>
       </c>
       <c r="B26" t="n">
-        <v>98334</v>
+        <v>79004</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>795427</v>
+        <v>795428</v>
       </c>
       <c r="R26" t="n">
-        <v>7292083</v>
+        <v>7292266</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,7 +3230,7 @@
         <v>125919207</v>
       </c>
       <c r="B27" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>125919136</v>
       </c>
       <c r="B28" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>125920110</v>
       </c>
       <c r="B29" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -1698,37 +1698,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125923834</v>
+        <v>125923726</v>
       </c>
       <c r="B12" t="n">
-        <v>91232</v>
+        <v>98338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1736,13 +1741,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>795428</v>
+        <v>795291</v>
       </c>
       <c r="R12" t="n">
-        <v>7292065</v>
+        <v>7291954</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1799,42 +1804,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125923726</v>
+        <v>125923834</v>
       </c>
       <c r="B13" t="n">
-        <v>98338</v>
+        <v>91232</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>795291</v>
+        <v>795428</v>
       </c>
       <c r="R13" t="n">
-        <v>7291954</v>
+        <v>7292065</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2108,37 +2108,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125923669</v>
+        <v>125923558</v>
       </c>
       <c r="B16" t="n">
-        <v>79004</v>
+        <v>98338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2146,10 +2151,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>795323</v>
+        <v>795338</v>
       </c>
       <c r="R16" t="n">
-        <v>7292029</v>
+        <v>7292138</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2209,7 +2214,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125923612</v>
+        <v>125923669</v>
       </c>
       <c r="B17" t="n">
         <v>79004</v>
@@ -2247,10 +2252,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>795337</v>
+        <v>795323</v>
       </c>
       <c r="R17" t="n">
-        <v>7292137</v>
+        <v>7292029</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2310,42 +2315,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125923558</v>
+        <v>125923612</v>
       </c>
       <c r="B18" t="n">
-        <v>98338</v>
+        <v>79004</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>795338</v>
+        <v>795337</v>
       </c>
       <c r="R18" t="n">
-        <v>7292138</v>
+        <v>7292137</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125923757</v>
       </c>
       <c r="B2" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>125923656</v>
       </c>
       <c r="B7" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>125923682</v>
       </c>
       <c r="B8" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>125919680</v>
       </c>
       <c r="B9" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,48 +1495,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125920922</v>
+        <v>125923769</v>
       </c>
       <c r="B10" t="n">
-        <v>79004</v>
+        <v>98339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Skog , Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>795257</v>
+        <v>795443</v>
       </c>
       <c r="R10" t="n">
-        <v>7292021</v>
+        <v>7292063</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1574,74 +1582,67 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125923769</v>
+        <v>125920922</v>
       </c>
       <c r="B11" t="n">
-        <v>98338</v>
+        <v>79004</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skog , Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>795443</v>
+        <v>795257</v>
       </c>
       <c r="R11" t="n">
-        <v>7292063</v>
+        <v>7292021</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1679,19 +1680,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1701,7 +1701,7 @@
         <v>125923726</v>
       </c>
       <c r="B12" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>125923482</v>
       </c>
       <c r="B14" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>125923558</v>
       </c>
       <c r="B16" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>125923742</v>
       </c>
       <c r="B19" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2522,37 +2522,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125923694</v>
+        <v>125923795</v>
       </c>
       <c r="B20" t="n">
-        <v>79004</v>
+        <v>98339</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2560,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>795304</v>
+        <v>795418</v>
       </c>
       <c r="R20" t="n">
-        <v>7291985</v>
+        <v>7292007</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2623,42 +2628,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125923795</v>
+        <v>125923694</v>
       </c>
       <c r="B21" t="n">
-        <v>98338</v>
+        <v>79004</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>795418</v>
+        <v>795304</v>
       </c>
       <c r="R21" t="n">
-        <v>7292007</v>
+        <v>7291985</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2729,48 +2729,51 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125920167</v>
+        <v>125923644</v>
       </c>
       <c r="B22" t="n">
-        <v>79979</v>
+        <v>79004</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>795457</v>
+        <v>795314</v>
       </c>
       <c r="R22" t="n">
-        <v>7292262</v>
+        <v>7292076</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2808,69 +2811,67 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125923644</v>
+        <v>125920167</v>
       </c>
       <c r="B23" t="n">
-        <v>79004</v>
+        <v>79979</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>795314</v>
+        <v>795457</v>
       </c>
       <c r="R23" t="n">
-        <v>7292076</v>
+        <v>7292262</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2908,19 +2909,18 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2930,7 +2930,7 @@
         <v>125923784</v>
       </c>
       <c r="B24" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,45 +3033,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125920695</v>
+        <v>125920335</v>
       </c>
       <c r="B25" t="n">
-        <v>98338</v>
+        <v>79004</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>795427</v>
+        <v>795428</v>
       </c>
       <c r="R25" t="n">
-        <v>7292083</v>
+        <v>7292266</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3130,45 +3130,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125920335</v>
+        <v>125920695</v>
       </c>
       <c r="B26" t="n">
-        <v>79004</v>
+        <v>98339</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>795428</v>
+        <v>795427</v>
       </c>
       <c r="R26" t="n">
-        <v>7292266</v>
+        <v>7292083</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,7 +3230,7 @@
         <v>125919207</v>
       </c>
       <c r="B27" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>125919136</v>
       </c>
       <c r="B28" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>125920110</v>
       </c>
       <c r="B29" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125920370</v>
+        <v>125923704</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>79004</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,37 +792,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>795431</v>
+        <v>795285</v>
       </c>
       <c r="R3" t="n">
-        <v>7292149</v>
+        <v>7291972</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,25 +863,26 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125923704</v>
+        <v>125923592</v>
       </c>
       <c r="B4" t="n">
         <v>79004</v>
@@ -916,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>795285</v>
+        <v>795338</v>
       </c>
       <c r="R4" t="n">
-        <v>7291972</v>
+        <v>7292144</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -979,7 +983,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125923592</v>
+        <v>125920247</v>
       </c>
       <c r="B5" t="n">
         <v>79004</v>
@@ -1008,22 +1012,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>795338</v>
+        <v>795441</v>
       </c>
       <c r="R5" t="n">
-        <v>7292144</v>
+        <v>7292235</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,29 +1062,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125920247</v>
+        <v>125920370</v>
       </c>
       <c r="B6" t="n">
-        <v>79004</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,34 +1091,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>795441</v>
+        <v>795431</v>
       </c>
       <c r="R6" t="n">
-        <v>7292235</v>
+        <v>7292149</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1698,37 +1698,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125923726</v>
+        <v>125923482</v>
       </c>
       <c r="B12" t="n">
-        <v>98339</v>
+        <v>98360</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1741,10 +1741,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>795291</v>
+        <v>795454</v>
       </c>
       <c r="R12" t="n">
-        <v>7291954</v>
+        <v>7292235</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1905,37 +1905,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125923482</v>
+        <v>125923726</v>
       </c>
       <c r="B14" t="n">
-        <v>98360</v>
+        <v>98339</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>795454</v>
+        <v>795291</v>
       </c>
       <c r="R14" t="n">
-        <v>7292235</v>
+        <v>7291954</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2108,42 +2108,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125923558</v>
+        <v>125923669</v>
       </c>
       <c r="B16" t="n">
-        <v>98339</v>
+        <v>79004</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2151,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>795338</v>
+        <v>795323</v>
       </c>
       <c r="R16" t="n">
-        <v>7292138</v>
+        <v>7292029</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2214,7 +2209,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125923669</v>
+        <v>125923612</v>
       </c>
       <c r="B17" t="n">
         <v>79004</v>
@@ -2252,10 +2247,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>795323</v>
+        <v>795337</v>
       </c>
       <c r="R17" t="n">
-        <v>7292029</v>
+        <v>7292137</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2315,37 +2310,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125923612</v>
+        <v>125923558</v>
       </c>
       <c r="B18" t="n">
-        <v>79004</v>
+        <v>98339</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>795337</v>
+        <v>795338</v>
       </c>
       <c r="R18" t="n">
-        <v>7292137</v>
+        <v>7292138</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2522,42 +2522,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125923795</v>
+        <v>125923694</v>
       </c>
       <c r="B20" t="n">
-        <v>98339</v>
+        <v>79004</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2565,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>795418</v>
+        <v>795304</v>
       </c>
       <c r="R20" t="n">
-        <v>7292007</v>
+        <v>7291985</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2628,37 +2623,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125923694</v>
+        <v>125923795</v>
       </c>
       <c r="B21" t="n">
-        <v>79004</v>
+        <v>98339</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>795304</v>
+        <v>795418</v>
       </c>
       <c r="R21" t="n">
-        <v>7291985</v>
+        <v>7292007</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -3033,45 +3033,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125920335</v>
+        <v>125920695</v>
       </c>
       <c r="B25" t="n">
-        <v>79004</v>
+        <v>98339</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>795428</v>
+        <v>795427</v>
       </c>
       <c r="R25" t="n">
-        <v>7292266</v>
+        <v>7292083</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3130,45 +3130,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125920695</v>
+        <v>125920335</v>
       </c>
       <c r="B26" t="n">
-        <v>98339</v>
+        <v>79004</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>795427</v>
+        <v>795428</v>
       </c>
       <c r="R26" t="n">
-        <v>7292083</v>
+        <v>7292266</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125923757</v>
       </c>
       <c r="B2" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125923704</v>
+        <v>125920370</v>
       </c>
       <c r="B3" t="n">
-        <v>79004</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,40 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>795285</v>
+        <v>795431</v>
       </c>
       <c r="R3" t="n">
-        <v>7291972</v>
+        <v>7292149</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,29 +860,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125923592</v>
+        <v>125923704</v>
       </c>
       <c r="B4" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>795338</v>
+        <v>795285</v>
       </c>
       <c r="R4" t="n">
-        <v>7292144</v>
+        <v>7291972</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -983,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125920247</v>
+        <v>125923592</v>
       </c>
       <c r="B5" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,19 +1008,22 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>795441</v>
+        <v>795338</v>
       </c>
       <c r="R5" t="n">
-        <v>7292235</v>
+        <v>7292144</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1062,28 +1061,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125920370</v>
+        <v>125920247</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>79005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,34 +1091,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>795431</v>
+        <v>795441</v>
       </c>
       <c r="R6" t="n">
-        <v>7292149</v>
+        <v>7292235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,7 +1180,7 @@
         <v>125923656</v>
       </c>
       <c r="B7" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>125923682</v>
       </c>
       <c r="B8" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>125919680</v>
       </c>
       <c r="B9" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,56 +1495,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125923769</v>
+        <v>125920922</v>
       </c>
       <c r="B10" t="n">
-        <v>98339</v>
+        <v>79005</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skog , Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>795443</v>
+        <v>795257</v>
       </c>
       <c r="R10" t="n">
-        <v>7292063</v>
+        <v>7292021</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1582,67 +1574,74 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125920922</v>
+        <v>125923769</v>
       </c>
       <c r="B11" t="n">
-        <v>79004</v>
+        <v>98341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Skog , Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>795257</v>
+        <v>795443</v>
       </c>
       <c r="R11" t="n">
-        <v>7292021</v>
+        <v>7292063</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1680,60 +1679,56 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125923482</v>
+        <v>125923834</v>
       </c>
       <c r="B12" t="n">
-        <v>98360</v>
+        <v>91234</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1741,13 +1736,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>795454</v>
+        <v>795428</v>
       </c>
       <c r="R12" t="n">
-        <v>7292235</v>
+        <v>7292065</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1804,37 +1799,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125923834</v>
+        <v>125923726</v>
       </c>
       <c r="B13" t="n">
-        <v>91232</v>
+        <v>98341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1842,13 +1842,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>795428</v>
+        <v>795291</v>
       </c>
       <c r="R13" t="n">
-        <v>7292065</v>
+        <v>7291954</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1905,37 +1905,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125923726</v>
+        <v>125923482</v>
       </c>
       <c r="B14" t="n">
-        <v>98339</v>
+        <v>98362</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>795291</v>
+        <v>795454</v>
       </c>
       <c r="R14" t="n">
-        <v>7291954</v>
+        <v>7292235</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2014,7 +2014,7 @@
         <v>125920880</v>
       </c>
       <c r="B15" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>125923669</v>
       </c>
       <c r="B16" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>125923612</v>
       </c>
       <c r="B17" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>125923558</v>
       </c>
       <c r="B18" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>125923742</v>
       </c>
       <c r="B19" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2522,37 +2522,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125923694</v>
+        <v>125923795</v>
       </c>
       <c r="B20" t="n">
-        <v>79004</v>
+        <v>98341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2560,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>795304</v>
+        <v>795418</v>
       </c>
       <c r="R20" t="n">
-        <v>7291985</v>
+        <v>7292007</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2623,42 +2628,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125923795</v>
+        <v>125923694</v>
       </c>
       <c r="B21" t="n">
-        <v>98339</v>
+        <v>79005</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>795418</v>
+        <v>795304</v>
       </c>
       <c r="R21" t="n">
-        <v>7292007</v>
+        <v>7291985</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2732,7 +2732,7 @@
         <v>125923644</v>
       </c>
       <c r="B22" t="n">
-        <v>79004</v>
+        <v>79005</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>125920167</v>
       </c>
       <c r="B23" t="n">
-        <v>79979</v>
+        <v>79980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>125923784</v>
       </c>
       <c r="B24" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3033,45 +3033,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125920695</v>
+        <v>125920335</v>
       </c>
       <c r="B25" t="n">
-        <v>98339</v>
+        <v>79005</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>795427</v>
+        <v>795428</v>
       </c>
       <c r="R25" t="n">
-        <v>7292083</v>
+        <v>7292266</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3130,45 +3130,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125920335</v>
+        <v>125920695</v>
       </c>
       <c r="B26" t="n">
-        <v>79004</v>
+        <v>98341</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>795428</v>
+        <v>795427</v>
       </c>
       <c r="R26" t="n">
-        <v>7292266</v>
+        <v>7292083</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,7 +3230,7 @@
         <v>125919207</v>
       </c>
       <c r="B27" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>125919136</v>
       </c>
       <c r="B28" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>125920110</v>
       </c>
       <c r="B29" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -2729,51 +2729,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125923644</v>
+        <v>125920167</v>
       </c>
       <c r="B22" t="n">
-        <v>79005</v>
+        <v>79980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>795314</v>
+        <v>795457</v>
       </c>
       <c r="R22" t="n">
-        <v>7292076</v>
+        <v>7292262</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2811,67 +2808,69 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125920167</v>
+        <v>125923644</v>
       </c>
       <c r="B23" t="n">
-        <v>79980</v>
+        <v>79005</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>795457</v>
+        <v>795314</v>
       </c>
       <c r="R23" t="n">
-        <v>7292262</v>
+        <v>7292076</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2909,18 +2908,19 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3033,45 +3033,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125920335</v>
+        <v>125920695</v>
       </c>
       <c r="B25" t="n">
-        <v>79005</v>
+        <v>98341</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>795428</v>
+        <v>795427</v>
       </c>
       <c r="R25" t="n">
-        <v>7292266</v>
+        <v>7292083</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3130,45 +3130,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125920695</v>
+        <v>125920335</v>
       </c>
       <c r="B26" t="n">
-        <v>98341</v>
+        <v>79005</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>795427</v>
+        <v>795428</v>
       </c>
       <c r="R26" t="n">
-        <v>7292083</v>
+        <v>7292266</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125923757</v>
       </c>
       <c r="B2" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125920370</v>
+        <v>125923704</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,37 +792,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>795431</v>
+        <v>795285</v>
       </c>
       <c r="R3" t="n">
-        <v>7292149</v>
+        <v>7291972</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,25 +863,26 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125923704</v>
+        <v>125923592</v>
       </c>
       <c r="B4" t="n">
         <v>79005</v>
@@ -916,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>795285</v>
+        <v>795338</v>
       </c>
       <c r="R4" t="n">
-        <v>7291972</v>
+        <v>7292144</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -979,7 +983,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125923592</v>
+        <v>125920247</v>
       </c>
       <c r="B5" t="n">
         <v>79005</v>
@@ -1008,22 +1012,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>795338</v>
+        <v>795441</v>
       </c>
       <c r="R5" t="n">
-        <v>7292144</v>
+        <v>7292235</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,29 +1062,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125920247</v>
+        <v>125920370</v>
       </c>
       <c r="B6" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,34 +1091,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>795441</v>
+        <v>795431</v>
       </c>
       <c r="R6" t="n">
-        <v>7292235</v>
+        <v>7292149</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,7 +1180,7 @@
         <v>125923656</v>
       </c>
       <c r="B7" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>125923682</v>
       </c>
       <c r="B8" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>125919680</v>
       </c>
       <c r="B9" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>125923769</v>
       </c>
       <c r="B11" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,37 +1698,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125923834</v>
+        <v>125923726</v>
       </c>
       <c r="B12" t="n">
-        <v>91234</v>
+        <v>98343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1736,13 +1741,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>795428</v>
+        <v>795291</v>
       </c>
       <c r="R12" t="n">
-        <v>7292065</v>
+        <v>7291954</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1799,37 +1804,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125923726</v>
+        <v>125923482</v>
       </c>
       <c r="B13" t="n">
-        <v>98341</v>
+        <v>98364</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1842,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>795291</v>
+        <v>795454</v>
       </c>
       <c r="R13" t="n">
-        <v>7291954</v>
+        <v>7292235</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1905,42 +1910,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125923482</v>
+        <v>125923834</v>
       </c>
       <c r="B14" t="n">
-        <v>98362</v>
+        <v>91236</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>795454</v>
+        <v>795428</v>
       </c>
       <c r="R14" t="n">
-        <v>7292235</v>
+        <v>7292065</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>125923558</v>
       </c>
       <c r="B18" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>125923742</v>
       </c>
       <c r="B19" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2522,42 +2522,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125923795</v>
+        <v>125923694</v>
       </c>
       <c r="B20" t="n">
-        <v>98341</v>
+        <v>79005</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2565,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>795418</v>
+        <v>795304</v>
       </c>
       <c r="R20" t="n">
-        <v>7292007</v>
+        <v>7291985</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2628,37 +2623,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125923694</v>
+        <v>125923795</v>
       </c>
       <c r="B21" t="n">
-        <v>79005</v>
+        <v>98343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>795304</v>
+        <v>795418</v>
       </c>
       <c r="R21" t="n">
-        <v>7291985</v>
+        <v>7292007</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2930,7 +2930,7 @@
         <v>125923784</v>
       </c>
       <c r="B24" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>125920695</v>
       </c>
       <c r="B25" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>125919207</v>
       </c>
       <c r="B27" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>125919136</v>
       </c>
       <c r="B28" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>125920110</v>
       </c>
       <c r="B29" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -3033,45 +3033,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125920695</v>
+        <v>125920335</v>
       </c>
       <c r="B25" t="n">
-        <v>98343</v>
+        <v>79005</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>795427</v>
+        <v>795428</v>
       </c>
       <c r="R25" t="n">
-        <v>7292083</v>
+        <v>7292266</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3130,45 +3130,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125920335</v>
+        <v>125920695</v>
       </c>
       <c r="B26" t="n">
-        <v>79005</v>
+        <v>98343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>795428</v>
+        <v>795427</v>
       </c>
       <c r="R26" t="n">
-        <v>7292266</v>
+        <v>7292083</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125923757</v>
       </c>
       <c r="B2" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125923704</v>
+        <v>125920370</v>
       </c>
       <c r="B3" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,40 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>795285</v>
+        <v>795431</v>
       </c>
       <c r="R3" t="n">
-        <v>7291972</v>
+        <v>7292149</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,26 +860,25 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125923592</v>
+        <v>125923704</v>
       </c>
       <c r="B4" t="n">
         <v>79005</v>
@@ -920,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>795338</v>
+        <v>795285</v>
       </c>
       <c r="R4" t="n">
-        <v>7292144</v>
+        <v>7291972</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -983,7 +979,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125920247</v>
+        <v>125923592</v>
       </c>
       <c r="B5" t="n">
         <v>79005</v>
@@ -1012,19 +1008,22 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>795441</v>
+        <v>795338</v>
       </c>
       <c r="R5" t="n">
-        <v>7292235</v>
+        <v>7292144</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1062,28 +1061,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125920370</v>
+        <v>125920247</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>79005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,34 +1091,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>795431</v>
+        <v>795441</v>
       </c>
       <c r="R6" t="n">
-        <v>7292149</v>
+        <v>7292235</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,7 +1180,7 @@
         <v>125923656</v>
       </c>
       <c r="B7" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>125923682</v>
       </c>
       <c r="B8" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>125919680</v>
       </c>
       <c r="B9" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,48 +1495,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125920922</v>
+        <v>125923769</v>
       </c>
       <c r="B10" t="n">
-        <v>79005</v>
+        <v>98345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Skog , Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>795257</v>
+        <v>795443</v>
       </c>
       <c r="R10" t="n">
-        <v>7292021</v>
+        <v>7292063</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1574,74 +1582,67 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125923769</v>
+        <v>125920922</v>
       </c>
       <c r="B11" t="n">
-        <v>98343</v>
+        <v>79005</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skog , Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>795443</v>
+        <v>795257</v>
       </c>
       <c r="R11" t="n">
-        <v>7292063</v>
+        <v>7292021</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1679,61 +1680,55 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125923726</v>
+        <v>125923834</v>
       </c>
       <c r="B12" t="n">
-        <v>98343</v>
+        <v>91238</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1741,13 +1736,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>795291</v>
+        <v>795428</v>
       </c>
       <c r="R12" t="n">
-        <v>7291954</v>
+        <v>7292065</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1807,7 +1802,7 @@
         <v>125923482</v>
       </c>
       <c r="B13" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1910,37 +1905,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125923834</v>
+        <v>125923726</v>
       </c>
       <c r="B14" t="n">
-        <v>91236</v>
+        <v>98345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>795428</v>
+        <v>795291</v>
       </c>
       <c r="R14" t="n">
-        <v>7292065</v>
+        <v>7291954</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2108,37 +2108,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125923669</v>
+        <v>125923558</v>
       </c>
       <c r="B16" t="n">
-        <v>79005</v>
+        <v>98345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2146,10 +2151,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>795323</v>
+        <v>795338</v>
       </c>
       <c r="R16" t="n">
-        <v>7292029</v>
+        <v>7292138</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2209,7 +2214,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125923612</v>
+        <v>125923669</v>
       </c>
       <c r="B17" t="n">
         <v>79005</v>
@@ -2247,10 +2252,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>795337</v>
+        <v>795323</v>
       </c>
       <c r="R17" t="n">
-        <v>7292137</v>
+        <v>7292029</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2310,42 +2315,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125923558</v>
+        <v>125923612</v>
       </c>
       <c r="B18" t="n">
-        <v>98343</v>
+        <v>79005</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>795338</v>
+        <v>795337</v>
       </c>
       <c r="R18" t="n">
-        <v>7292138</v>
+        <v>7292137</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2419,7 +2419,7 @@
         <v>125923742</v>
       </c>
       <c r="B19" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2522,37 +2522,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125923694</v>
+        <v>125923795</v>
       </c>
       <c r="B20" t="n">
-        <v>79005</v>
+        <v>98345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2560,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>795304</v>
+        <v>795418</v>
       </c>
       <c r="R20" t="n">
-        <v>7291985</v>
+        <v>7292007</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2623,42 +2628,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125923795</v>
+        <v>125923694</v>
       </c>
       <c r="B21" t="n">
-        <v>98343</v>
+        <v>79005</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>795418</v>
+        <v>795304</v>
       </c>
       <c r="R21" t="n">
-        <v>7292007</v>
+        <v>7291985</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2729,48 +2729,51 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125920167</v>
+        <v>125923644</v>
       </c>
       <c r="B22" t="n">
-        <v>79980</v>
+        <v>79005</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>795457</v>
+        <v>795314</v>
       </c>
       <c r="R22" t="n">
-        <v>7292262</v>
+        <v>7292076</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2808,69 +2811,67 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125923644</v>
+        <v>125920167</v>
       </c>
       <c r="B23" t="n">
-        <v>79005</v>
+        <v>79980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>795314</v>
+        <v>795457</v>
       </c>
       <c r="R23" t="n">
-        <v>7292076</v>
+        <v>7292262</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2908,19 +2909,18 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2930,7 +2930,7 @@
         <v>125923784</v>
       </c>
       <c r="B24" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>125920695</v>
       </c>
       <c r="B26" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>125919207</v>
       </c>
       <c r="B27" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>125919136</v>
       </c>
       <c r="B28" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>125920110</v>
       </c>
       <c r="B29" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -1495,56 +1495,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125923769</v>
+        <v>125920922</v>
       </c>
       <c r="B10" t="n">
-        <v>98345</v>
+        <v>79005</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skog , Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>795443</v>
+        <v>795257</v>
       </c>
       <c r="R10" t="n">
-        <v>7292063</v>
+        <v>7292021</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1582,67 +1574,74 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125920922</v>
+        <v>125923769</v>
       </c>
       <c r="B11" t="n">
-        <v>79005</v>
+        <v>98345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Skog , Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>795257</v>
+        <v>795443</v>
       </c>
       <c r="R11" t="n">
-        <v>7292021</v>
+        <v>7292063</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1680,18 +1679,19 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125923757</v>
       </c>
       <c r="B2" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>125920370</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125923704</v>
+        <v>125923592</v>
       </c>
       <c r="B4" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>795285</v>
+        <v>795338</v>
       </c>
       <c r="R4" t="n">
-        <v>7291972</v>
+        <v>7292144</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -979,10 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125923592</v>
+        <v>125923704</v>
       </c>
       <c r="B5" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>795338</v>
+        <v>795285</v>
       </c>
       <c r="R5" t="n">
-        <v>7292144</v>
+        <v>7291972</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1083,7 +1083,7 @@
         <v>125920247</v>
       </c>
       <c r="B6" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>125923656</v>
       </c>
       <c r="B7" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>125923682</v>
       </c>
       <c r="B8" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>125919680</v>
       </c>
       <c r="B9" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>125920922</v>
       </c>
       <c r="B10" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>125923769</v>
       </c>
       <c r="B11" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>125923834</v>
       </c>
       <c r="B12" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,37 +1799,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125923482</v>
+        <v>125923726</v>
       </c>
       <c r="B13" t="n">
-        <v>98366</v>
+        <v>98349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>795454</v>
+        <v>795291</v>
       </c>
       <c r="R13" t="n">
-        <v>7292235</v>
+        <v>7291954</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1905,37 +1905,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125923726</v>
+        <v>125923482</v>
       </c>
       <c r="B14" t="n">
-        <v>98345</v>
+        <v>98370</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>795291</v>
+        <v>795454</v>
       </c>
       <c r="R14" t="n">
-        <v>7291954</v>
+        <v>7292235</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2014,7 +2014,7 @@
         <v>125920880</v>
       </c>
       <c r="B15" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>125923558</v>
       </c>
       <c r="B16" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125923669</v>
+        <v>125923612</v>
       </c>
       <c r="B17" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>795323</v>
+        <v>795337</v>
       </c>
       <c r="R17" t="n">
-        <v>7292029</v>
+        <v>7292137</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2315,10 +2315,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125923612</v>
+        <v>125923669</v>
       </c>
       <c r="B18" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>795337</v>
+        <v>795323</v>
       </c>
       <c r="R18" t="n">
-        <v>7292137</v>
+        <v>7292029</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2419,7 +2419,7 @@
         <v>125923742</v>
       </c>
       <c r="B19" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>125923795</v>
       </c>
       <c r="B20" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>125923694</v>
       </c>
       <c r="B21" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2729,51 +2729,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125923644</v>
+        <v>125920167</v>
       </c>
       <c r="B22" t="n">
-        <v>79005</v>
+        <v>79984</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>795314</v>
+        <v>795457</v>
       </c>
       <c r="R22" t="n">
-        <v>7292076</v>
+        <v>7292262</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2811,67 +2808,69 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125920167</v>
+        <v>125923644</v>
       </c>
       <c r="B23" t="n">
-        <v>79980</v>
+        <v>79009</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>795457</v>
+        <v>795314</v>
       </c>
       <c r="R23" t="n">
-        <v>7292262</v>
+        <v>7292076</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2909,18 +2908,19 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2930,7 +2930,7 @@
         <v>125923784</v>
       </c>
       <c r="B24" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>125920335</v>
       </c>
       <c r="B25" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>125920695</v>
       </c>
       <c r="B26" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>125919207</v>
       </c>
       <c r="B27" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>125919136</v>
       </c>
       <c r="B28" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>125920110</v>
       </c>
       <c r="B29" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -2108,42 +2108,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125923558</v>
+        <v>125923612</v>
       </c>
       <c r="B16" t="n">
-        <v>98349</v>
+        <v>79009</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2151,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>795338</v>
+        <v>795337</v>
       </c>
       <c r="R16" t="n">
-        <v>7292138</v>
+        <v>7292137</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2214,7 +2209,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125923612</v>
+        <v>125923669</v>
       </c>
       <c r="B17" t="n">
         <v>79009</v>
@@ -2252,10 +2247,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>795337</v>
+        <v>795323</v>
       </c>
       <c r="R17" t="n">
-        <v>7292137</v>
+        <v>7292029</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2315,37 +2310,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125923669</v>
+        <v>125923558</v>
       </c>
       <c r="B18" t="n">
-        <v>79009</v>
+        <v>98349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>795323</v>
+        <v>795338</v>
       </c>
       <c r="R18" t="n">
-        <v>7292029</v>
+        <v>7292138</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125923757</v>
       </c>
       <c r="B2" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125920370</v>
+        <v>125923704</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,37 +792,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>795431</v>
+        <v>795285</v>
       </c>
       <c r="R3" t="n">
-        <v>7292149</v>
+        <v>7291972</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,18 +863,19 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -979,7 +983,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125923704</v>
+        <v>125920247</v>
       </c>
       <c r="B5" t="n">
         <v>79009</v>
@@ -1008,22 +1012,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>795285</v>
+        <v>795441</v>
       </c>
       <c r="R5" t="n">
-        <v>7291972</v>
+        <v>7292235</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,29 +1062,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125920247</v>
+        <v>125920370</v>
       </c>
       <c r="B6" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,34 +1091,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>795441</v>
+        <v>795431</v>
       </c>
       <c r="R6" t="n">
-        <v>7292235</v>
+        <v>7292149</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,7 +1180,7 @@
         <v>125923656</v>
       </c>
       <c r="B7" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>125923682</v>
       </c>
       <c r="B8" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>125919680</v>
       </c>
       <c r="B9" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>125923769</v>
       </c>
       <c r="B11" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,37 +1799,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125923726</v>
+        <v>125923482</v>
       </c>
       <c r="B13" t="n">
-        <v>98349</v>
+        <v>98373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>795291</v>
+        <v>795454</v>
       </c>
       <c r="R13" t="n">
-        <v>7291954</v>
+        <v>7292235</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1905,37 +1905,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125923482</v>
+        <v>125923726</v>
       </c>
       <c r="B14" t="n">
-        <v>98370</v>
+        <v>98352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>795454</v>
+        <v>795291</v>
       </c>
       <c r="R14" t="n">
-        <v>7292235</v>
+        <v>7291954</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125923612</v>
+        <v>125923669</v>
       </c>
       <c r="B16" t="n">
         <v>79009</v>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>795337</v>
+        <v>795323</v>
       </c>
       <c r="R16" t="n">
-        <v>7292137</v>
+        <v>7292029</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2209,7 +2209,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125923669</v>
+        <v>125923612</v>
       </c>
       <c r="B17" t="n">
         <v>79009</v>
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>795323</v>
+        <v>795337</v>
       </c>
       <c r="R17" t="n">
-        <v>7292029</v>
+        <v>7292137</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2313,7 +2313,7 @@
         <v>125923558</v>
       </c>
       <c r="B18" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>125923742</v>
       </c>
       <c r="B19" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2522,42 +2522,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125923795</v>
+        <v>125923694</v>
       </c>
       <c r="B20" t="n">
-        <v>98349</v>
+        <v>79009</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2565,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>795418</v>
+        <v>795304</v>
       </c>
       <c r="R20" t="n">
-        <v>7292007</v>
+        <v>7291985</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2628,37 +2623,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125923694</v>
+        <v>125923795</v>
       </c>
       <c r="B21" t="n">
-        <v>79009</v>
+        <v>98352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>795304</v>
+        <v>795418</v>
       </c>
       <c r="R21" t="n">
-        <v>7291985</v>
+        <v>7292007</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2729,48 +2729,51 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125920167</v>
+        <v>125923644</v>
       </c>
       <c r="B22" t="n">
-        <v>79984</v>
+        <v>79009</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>795457</v>
+        <v>795314</v>
       </c>
       <c r="R22" t="n">
-        <v>7292262</v>
+        <v>7292076</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2808,69 +2811,67 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125923644</v>
+        <v>125920167</v>
       </c>
       <c r="B23" t="n">
-        <v>79009</v>
+        <v>79984</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>795314</v>
+        <v>795457</v>
       </c>
       <c r="R23" t="n">
-        <v>7292076</v>
+        <v>7292262</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2908,19 +2909,18 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2930,7 +2930,7 @@
         <v>125923784</v>
       </c>
       <c r="B24" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>125920695</v>
       </c>
       <c r="B26" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>125919207</v>
       </c>
       <c r="B27" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>125919136</v>
       </c>
       <c r="B28" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>125920110</v>
       </c>
       <c r="B29" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125923704</v>
+        <v>125920247</v>
       </c>
       <c r="B3" t="n">
         <v>79009</v>
@@ -810,22 +810,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>795285</v>
+        <v>795441</v>
       </c>
       <c r="R3" t="n">
-        <v>7291972</v>
+        <v>7292235</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,29 +860,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125923592</v>
+        <v>125920370</v>
       </c>
       <c r="B4" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,40 +889,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>795338</v>
+        <v>795431</v>
       </c>
       <c r="R4" t="n">
-        <v>7292144</v>
+        <v>7292149</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,26 +957,25 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125920247</v>
+        <v>125923704</v>
       </c>
       <c r="B5" t="n">
         <v>79009</v>
@@ -1012,19 +1004,22 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>795441</v>
+        <v>795285</v>
       </c>
       <c r="R5" t="n">
-        <v>7292235</v>
+        <v>7291972</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1062,28 +1057,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125920370</v>
+        <v>125923592</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,37 +1087,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>795431</v>
+        <v>795338</v>
       </c>
       <c r="R6" t="n">
-        <v>7292149</v>
+        <v>7292144</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1159,18 +1158,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1495,48 +1495,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125920922</v>
+        <v>125923769</v>
       </c>
       <c r="B10" t="n">
-        <v>79009</v>
+        <v>98352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Skog , Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>795257</v>
+        <v>795443</v>
       </c>
       <c r="R10" t="n">
-        <v>7292021</v>
+        <v>7292063</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1574,74 +1582,67 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125923769</v>
+        <v>125920922</v>
       </c>
       <c r="B11" t="n">
-        <v>98352</v>
+        <v>79009</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skog , Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>795443</v>
+        <v>795257</v>
       </c>
       <c r="R11" t="n">
-        <v>7292063</v>
+        <v>7292021</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1679,19 +1680,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125920247</v>
+        <v>125920370</v>
       </c>
       <c r="B3" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,34 +792,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>795441</v>
+        <v>795431</v>
       </c>
       <c r="R3" t="n">
-        <v>7292235</v>
+        <v>7292149</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125920370</v>
+        <v>125923704</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,37 +889,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>795431</v>
+        <v>795285</v>
       </c>
       <c r="R4" t="n">
-        <v>7292149</v>
+        <v>7291972</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,25 +960,26 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125923704</v>
+        <v>125923592</v>
       </c>
       <c r="B5" t="n">
         <v>79009</v>
@@ -1013,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>795285</v>
+        <v>795338</v>
       </c>
       <c r="R5" t="n">
-        <v>7291972</v>
+        <v>7292144</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1076,7 +1080,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125923592</v>
+        <v>125920247</v>
       </c>
       <c r="B6" t="n">
         <v>79009</v>
@@ -1105,22 +1109,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>795338</v>
+        <v>795441</v>
       </c>
       <c r="R6" t="n">
-        <v>7292144</v>
+        <v>7292235</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1158,19 +1159,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1799,37 +1799,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125923482</v>
+        <v>125923726</v>
       </c>
       <c r="B13" t="n">
-        <v>98373</v>
+        <v>98352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>795454</v>
+        <v>795291</v>
       </c>
       <c r="R13" t="n">
-        <v>7292235</v>
+        <v>7291954</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1905,37 +1905,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125923726</v>
+        <v>125923482</v>
       </c>
       <c r="B14" t="n">
-        <v>98352</v>
+        <v>98373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>795291</v>
+        <v>795454</v>
       </c>
       <c r="R14" t="n">
-        <v>7291954</v>
+        <v>7292235</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2522,37 +2522,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125923694</v>
+        <v>125923795</v>
       </c>
       <c r="B20" t="n">
-        <v>79009</v>
+        <v>98352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2560,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>795304</v>
+        <v>795418</v>
       </c>
       <c r="R20" t="n">
-        <v>7291985</v>
+        <v>7292007</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2623,42 +2628,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125923795</v>
+        <v>125923694</v>
       </c>
       <c r="B21" t="n">
-        <v>98352</v>
+        <v>79009</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>795418</v>
+        <v>795304</v>
       </c>
       <c r="R21" t="n">
-        <v>7292007</v>
+        <v>7291985</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2729,51 +2729,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125923644</v>
+        <v>125920167</v>
       </c>
       <c r="B22" t="n">
-        <v>79009</v>
+        <v>79984</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>795314</v>
+        <v>795457</v>
       </c>
       <c r="R22" t="n">
-        <v>7292076</v>
+        <v>7292262</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2811,67 +2808,69 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125920167</v>
+        <v>125923644</v>
       </c>
       <c r="B23" t="n">
-        <v>79984</v>
+        <v>79009</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>795457</v>
+        <v>795314</v>
       </c>
       <c r="R23" t="n">
-        <v>7292262</v>
+        <v>7292076</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2909,18 +2908,19 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125923757</v>
       </c>
       <c r="B2" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>125920370</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>125923704</v>
       </c>
       <c r="B4" t="n">
-        <v>79009</v>
+        <v>79012</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>125923592</v>
       </c>
       <c r="B5" t="n">
-        <v>79009</v>
+        <v>79012</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>125920247</v>
       </c>
       <c r="B6" t="n">
-        <v>79009</v>
+        <v>79012</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>125923656</v>
       </c>
       <c r="B7" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>125923682</v>
       </c>
       <c r="B8" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>125919680</v>
       </c>
       <c r="B9" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,56 +1495,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125923769</v>
+        <v>125920922</v>
       </c>
       <c r="B10" t="n">
-        <v>98352</v>
+        <v>79012</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skog , Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>795443</v>
+        <v>795257</v>
       </c>
       <c r="R10" t="n">
-        <v>7292063</v>
+        <v>7292021</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1582,67 +1574,74 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125920922</v>
+        <v>125923769</v>
       </c>
       <c r="B11" t="n">
-        <v>79009</v>
+        <v>98361</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Skog , Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>795257</v>
+        <v>795443</v>
       </c>
       <c r="R11" t="n">
-        <v>7292021</v>
+        <v>7292063</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1680,18 +1679,19 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1701,7 +1701,7 @@
         <v>125923834</v>
       </c>
       <c r="B12" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>125923726</v>
       </c>
       <c r="B13" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>125923482</v>
       </c>
       <c r="B14" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>125920880</v>
       </c>
       <c r="B15" t="n">
-        <v>79009</v>
+        <v>79012</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>125923669</v>
       </c>
       <c r="B16" t="n">
-        <v>79009</v>
+        <v>79012</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>125923612</v>
       </c>
       <c r="B17" t="n">
-        <v>79009</v>
+        <v>79012</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>125923558</v>
       </c>
       <c r="B18" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>125923742</v>
       </c>
       <c r="B19" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2522,42 +2522,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125923795</v>
+        <v>125923694</v>
       </c>
       <c r="B20" t="n">
-        <v>98352</v>
+        <v>79012</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2565,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>795418</v>
+        <v>795304</v>
       </c>
       <c r="R20" t="n">
-        <v>7292007</v>
+        <v>7291985</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2628,37 +2623,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125923694</v>
+        <v>125923795</v>
       </c>
       <c r="B21" t="n">
-        <v>79009</v>
+        <v>98361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>795304</v>
+        <v>795418</v>
       </c>
       <c r="R21" t="n">
-        <v>7291985</v>
+        <v>7292007</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2729,48 +2729,51 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125920167</v>
+        <v>125923644</v>
       </c>
       <c r="B22" t="n">
-        <v>79984</v>
+        <v>79012</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>795457</v>
+        <v>795314</v>
       </c>
       <c r="R22" t="n">
-        <v>7292262</v>
+        <v>7292076</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2808,69 +2811,67 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125923644</v>
+        <v>125920167</v>
       </c>
       <c r="B23" t="n">
-        <v>79009</v>
+        <v>79987</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>795314</v>
+        <v>795457</v>
       </c>
       <c r="R23" t="n">
-        <v>7292076</v>
+        <v>7292262</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2908,19 +2909,18 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2930,7 +2930,7 @@
         <v>125923784</v>
       </c>
       <c r="B24" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>125920335</v>
       </c>
       <c r="B25" t="n">
-        <v>79009</v>
+        <v>79012</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>125920695</v>
       </c>
       <c r="B26" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>125919207</v>
       </c>
       <c r="B27" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>125919136</v>
       </c>
       <c r="B28" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>125920110</v>
       </c>
       <c r="B29" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -2108,37 +2108,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125923669</v>
+        <v>125923558</v>
       </c>
       <c r="B16" t="n">
-        <v>79012</v>
+        <v>98361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2146,10 +2151,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>795323</v>
+        <v>795338</v>
       </c>
       <c r="R16" t="n">
-        <v>7292029</v>
+        <v>7292138</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2209,7 +2214,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125923612</v>
+        <v>125923669</v>
       </c>
       <c r="B17" t="n">
         <v>79012</v>
@@ -2247,10 +2252,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>795337</v>
+        <v>795323</v>
       </c>
       <c r="R17" t="n">
-        <v>7292137</v>
+        <v>7292029</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2310,42 +2315,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125923558</v>
+        <v>125923612</v>
       </c>
       <c r="B18" t="n">
-        <v>98361</v>
+        <v>79012</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>795338</v>
+        <v>795337</v>
       </c>
       <c r="R18" t="n">
-        <v>7292138</v>
+        <v>7292137</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -2108,42 +2108,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125923558</v>
+        <v>125923669</v>
       </c>
       <c r="B16" t="n">
-        <v>98361</v>
+        <v>79012</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2151,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>795338</v>
+        <v>795323</v>
       </c>
       <c r="R16" t="n">
-        <v>7292138</v>
+        <v>7292029</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2214,7 +2209,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125923669</v>
+        <v>125923612</v>
       </c>
       <c r="B17" t="n">
         <v>79012</v>
@@ -2252,10 +2247,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>795323</v>
+        <v>795337</v>
       </c>
       <c r="R17" t="n">
-        <v>7292029</v>
+        <v>7292137</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2315,37 +2310,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125923612</v>
+        <v>125923558</v>
       </c>
       <c r="B18" t="n">
-        <v>79012</v>
+        <v>98361</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>795337</v>
+        <v>795338</v>
       </c>
       <c r="R18" t="n">
-        <v>7292137</v>
+        <v>7292138</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2522,37 +2522,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125923694</v>
+        <v>125923795</v>
       </c>
       <c r="B20" t="n">
-        <v>79012</v>
+        <v>98361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2560,10 +2565,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>795304</v>
+        <v>795418</v>
       </c>
       <c r="R20" t="n">
-        <v>7291985</v>
+        <v>7292007</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2623,42 +2628,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125923795</v>
+        <v>125923694</v>
       </c>
       <c r="B21" t="n">
-        <v>98361</v>
+        <v>79012</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>795418</v>
+        <v>795304</v>
       </c>
       <c r="R21" t="n">
-        <v>7292007</v>
+        <v>7291985</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -1495,48 +1495,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125920922</v>
+        <v>125923769</v>
       </c>
       <c r="B10" t="n">
-        <v>79012</v>
+        <v>98361</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Skog , Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>795257</v>
+        <v>795443</v>
       </c>
       <c r="R10" t="n">
-        <v>7292021</v>
+        <v>7292063</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1574,74 +1582,67 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125923769</v>
+        <v>125920922</v>
       </c>
       <c r="B11" t="n">
-        <v>98361</v>
+        <v>79012</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skog , Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>795443</v>
+        <v>795257</v>
       </c>
       <c r="R11" t="n">
-        <v>7292063</v>
+        <v>7292021</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1679,19 +1680,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 18382-2025 artfynd.xlsx
+++ b/artfynd/A 18382-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125920370</v>
+        <v>125923704</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79012</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,37 +792,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
+          <t>Skog, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>795431</v>
+        <v>795285</v>
       </c>
       <c r="R3" t="n">
-        <v>7292149</v>
+        <v>7291972</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,25 +863,26 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Agnes Hjortsberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125923704</v>
+        <v>125923592</v>
       </c>
       <c r="B4" t="n">
         <v>79012</v>
@@ -916,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>795285</v>
+        <v>795338</v>
       </c>
       <c r="R4" t="n">
-        <v>7291972</v>
+        <v>7292144</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -979,7 +983,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125923592</v>
+        <v>125920247</v>
       </c>
       <c r="B5" t="n">
         <v>79012</v>
@@ -1008,22 +1012,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skog, Nb</t>
+          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>795338</v>
+        <v>795441</v>
       </c>
       <c r="R5" t="n">
-        <v>7292144</v>
+        <v>7292235</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,29 +1062,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Agnes Hjortsberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125920247</v>
+        <v>125920370</v>
       </c>
       <c r="B6" t="n">
-        <v>79012</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,34 +1091,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Klöverträskbackens naturreservat, Klöverträskbackens naturreservat, Nb</t>
+          <t>Karl-Öbergsberget, Karl-Öbergsberget, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>795441</v>
+        <v>795431</v>
       </c>
       <c r="R6" t="n">
-        <v>7292235</v>
+        <v>7292149</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2522,42 +2522,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125923795</v>
+        <v>125923694</v>
       </c>
       <c r="B20" t="n">
-        <v>98361</v>
+        <v>79012</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2565,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>795418</v>
+        <v>795304</v>
       </c>
       <c r="R20" t="n">
-        <v>7292007</v>
+        <v>7291985</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2628,37 +2623,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125923694</v>
+        <v>125923795</v>
       </c>
       <c r="B21" t="n">
-        <v>79012</v>
+        <v>98361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>795304</v>
+        <v>795418</v>
       </c>
       <c r="R21" t="n">
-        <v>7291985</v>
+        <v>7292007</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
